--- a/EntradaProductos_LETTA.xlsx
+++ b/EntradaProductos_LETTA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17900" windowHeight="13260"/>
+    <workbookView windowWidth="15740" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
   <si>
     <t>Code</t>
   </si>
@@ -85,205 +85,160 @@
     <t>Precio Promocion</t>
   </si>
   <si>
-    <t>LTA2171</t>
+    <t>LTA2206</t>
   </si>
   <si>
-    <t xml:space="preserve">Vestido </t>
+    <t>Tops /tallas-pequenas</t>
   </si>
   <si>
-    <t>Vestido espalda descubierta beige Lefties</t>
+    <t>Top off the shoulder acanalado negro H&amp;M</t>
   </si>
   <si>
     <t>Talla S</t>
   </si>
   <si>
-    <t>LTA2172</t>
+    <t>LTA2207</t>
+  </si>
+  <si>
+    <t>Top con escote en U negro H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2208</t>
+  </si>
+  <si>
+    <t>tops /tallas-grandes</t>
+  </si>
+  <si>
+    <t>Pulóver acanalado beige claro jaspeado H&amp;M</t>
+  </si>
+  <si>
+    <t>Talla L</t>
+  </si>
+  <si>
+    <t>LTA2210</t>
+  </si>
+  <si>
+    <t>Body de microfibra negro H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2212</t>
+  </si>
+  <si>
+    <t>Top sin mangas fruncido marrón H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2213</t>
+  </si>
+  <si>
+    <t>Top sin mangas acanalado azul marino H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2214</t>
+  </si>
+  <si>
+    <t>Top en punto pointille blanco con rayas H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2216</t>
+  </si>
+  <si>
+    <t>Pulóver acanalado cuello bote rojo teja H&amp;M</t>
+  </si>
+  <si>
+    <t>Talla XS</t>
+  </si>
+  <si>
+    <t>LTA2217</t>
+  </si>
+  <si>
+    <t>Pulóver de microfibra marrón oscuro H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2218</t>
+  </si>
+  <si>
+    <t>Top off the shoulder en punto acanalado blanco H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2219</t>
+  </si>
+  <si>
+    <t>Pulóver entallado traslúcido blanco H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2221</t>
+  </si>
+  <si>
+    <t>Pulóver entallado blanco con ribete azul marino H&amp;M</t>
+  </si>
+  <si>
+    <t>Talla XXS</t>
+  </si>
+  <si>
+    <t>LTA2222</t>
+  </si>
+  <si>
+    <t>Pulóver con escote U y tapeta de botones negro H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2223</t>
+  </si>
+  <si>
+    <t>Pulóver de microfibra blanco H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2224</t>
+  </si>
+  <si>
+    <t>Pulóver entallado de microfibra azul marino H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2225</t>
+  </si>
+  <si>
+    <t>Cárdigan de manga corta en punto fino negro H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2226</t>
+  </si>
+  <si>
+    <t>Top of the shoulder acanalado blanco H&amp;M</t>
+  </si>
+  <si>
+    <t>LTA2227</t>
+  </si>
+  <si>
+    <t>Tops /tallas-medianas</t>
+  </si>
+  <si>
+    <t>Pulóver corto algodón gris oscuro H&amp;M</t>
   </si>
   <si>
     <t>Talla M</t>
   </si>
   <si>
-    <t>LTA2173</t>
+    <t>LTA2228</t>
   </si>
   <si>
-    <t>Vestido espalda descubierta verde caqui Lefties</t>
+    <t>Pulóver de aalgodón azul marino Paris H&amp;M</t>
   </si>
   <si>
-    <t>LTA2174</t>
+    <t>LTA2229</t>
   </si>
   <si>
-    <t>Talla XS</t>
+    <t>Pulóver con estampado blanco Rio de Janeiro H&amp;M</t>
   </si>
   <si>
-    <t>LTA2175</t>
+    <t>LTA2230</t>
   </si>
   <si>
-    <t>LTA2176</t>
+    <t>Pulóver oversized azul marino Surf Club H&amp;M</t>
   </si>
   <si>
-    <t>Vestido espalda descubierta negro Lefties</t>
+    <t>LTA2232</t>
   </si>
   <si>
-    <t>LTA2177</t>
-  </si>
-  <si>
-    <t>Partes-de-abajo /tallas-medianas</t>
-  </si>
-  <si>
-    <t>Pantalón wide con pliegues beige Lefties</t>
-  </si>
-  <si>
-    <t>Talla S/M</t>
-  </si>
-  <si>
-    <t>LTA2178</t>
-  </si>
-  <si>
-    <t>Partes-de-abajo /tallas-grandes</t>
-  </si>
-  <si>
-    <t>Talla M/L</t>
-  </si>
-  <si>
-    <t>LTA2179</t>
-  </si>
-  <si>
-    <t>Talla L</t>
-  </si>
-  <si>
-    <t>LTA2180</t>
-  </si>
-  <si>
-    <t>Pantalón wide de vestir beige jaspeado Lefties</t>
-  </si>
-  <si>
-    <t>LTA2181</t>
-  </si>
-  <si>
-    <t>Pantalón wide leg de vestir rojo vivo Lefties</t>
-  </si>
-  <si>
-    <t>LTA2182</t>
-  </si>
-  <si>
-    <t>Pantalón wide leg de vestir negro Lefties</t>
-  </si>
-  <si>
-    <t>LTA2183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantalón wide de vestir con pliegues negro Lefties </t>
-  </si>
-  <si>
-    <t>LTA2184</t>
-  </si>
-  <si>
-    <t>Pantalón wide leg de vestir beige claro Lefties</t>
-  </si>
-  <si>
-    <t>LTA2185</t>
-  </si>
-  <si>
-    <t>Pantalón de vestir básico crema Lefties</t>
-  </si>
-  <si>
-    <t>LTA2186</t>
-  </si>
-  <si>
-    <t>Partes-de-abajo /tallas-pequenas</t>
-  </si>
-  <si>
-    <t>Pantalón de vestir básico verde olivo Lefties</t>
-  </si>
-  <si>
-    <t>LTA2187</t>
-  </si>
-  <si>
-    <t>Pantalón mini flare marrón Lefties</t>
-  </si>
-  <si>
-    <t>LTA2188</t>
-  </si>
-  <si>
-    <t>Pantalón de vestir básico rosa palo Lefities</t>
-  </si>
-  <si>
-    <t>LTA2189</t>
-  </si>
-  <si>
-    <t>Pantalón de vestir básco marrón topo Lefties</t>
-  </si>
-  <si>
-    <t>LTA2190</t>
-  </si>
-  <si>
-    <t>LTA2191</t>
-  </si>
-  <si>
-    <t>Pantalón rústico lazada verde caqui Lefties</t>
-  </si>
-  <si>
-    <t>LTA2192</t>
-  </si>
-  <si>
-    <t>LTA2193</t>
-  </si>
-  <si>
-    <t>LTA2194</t>
-  </si>
-  <si>
-    <t>Pantalón joggers de vestir verde caqui Lefties</t>
-  </si>
-  <si>
-    <t>LTA2195</t>
-  </si>
-  <si>
-    <t>Pantalón joggers de vestir negro Lefties</t>
-  </si>
-  <si>
-    <t>LTA2196</t>
-  </si>
-  <si>
-    <t>Pantalón básico de vestir beige oscuro Lefties</t>
-  </si>
-  <si>
-    <t>LTA2197</t>
-  </si>
-  <si>
-    <t>Pantalón de vestir ancho beige jaspeado Lefties</t>
-  </si>
-  <si>
-    <t>LTA2198</t>
-  </si>
-  <si>
-    <t>Pantalón en mezcla de lino con atadura azul claro Bershka</t>
-  </si>
-  <si>
-    <t>LTA2200</t>
-  </si>
-  <si>
-    <t>Pantalónde sarga con cordón de ajuste color topo H&amp;M</t>
-  </si>
-  <si>
-    <t>LTA2203</t>
-  </si>
-  <si>
-    <t>Pantalón en mezcla de lino con cordón de ajuste negro H&amp;M</t>
-  </si>
-  <si>
-    <t>LTA2204</t>
-  </si>
-  <si>
-    <t>Pantalón acampanado con raya marrón oscuro H&amp;M</t>
-  </si>
-  <si>
-    <t>Talla XL_12</t>
-  </si>
-  <si>
-    <t>LTA2205</t>
-  </si>
-  <si>
-    <t>Pantalón sastre amplio marrón oscuro H&amp;M</t>
+    <t>Top estilo corset negro con tirantes anudados</t>
   </si>
 </sst>
 </file>
@@ -293,13 +248,13 @@
   <numFmts count="9">
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.0"/>
     <numFmt numFmtId="177" formatCode="_ [$$-540A]* #,##0.00_ ;_ [$$-540A]* \-#,##0.00_ ;_ [$$-540A]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -344,23 +299,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,23 +315,47 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -412,9 +377,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,39 +392,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,15 +407,36 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -515,13 +470,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,85 +602,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,67 +632,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,6 +743,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -814,24 +784,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -850,164 +816,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1025,10 +980,10 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1044,7 +999,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="180" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1054,7 +1009,7 @@
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1064,7 +1019,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1073,7 +1028,7 @@
     <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1266,56 +1221,6 @@
         <row r="23">
           <cell r="A23" t="str">
             <v>UB0248</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>UB0254</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>UB0261</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>BU0271</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>BU0278</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>BU0282</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>BU0283</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>BU0321</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>YILHM0472</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>BU0378</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>BU0404</v>
           </cell>
         </row>
       </sheetData>
@@ -58746,7 +58651,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB66"/>
+  <dimension ref="A1:AB61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="2" customWidth="1"/>
@@ -58852,7 +58757,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G2" s="15">
         <v>1</v>
@@ -58865,18 +58770,13 @@
         <v>1</v>
       </c>
       <c r="J2" s="14"/>
-      <c r="K2" s="14">
-        <v>15</v>
-      </c>
+      <c r="K2" s="14"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
-      <c r="N2" s="14">
-        <f t="shared" ref="N2:N29" si="0">M2*1.5</f>
-        <v>0</v>
-      </c>
+      <c r="N2" s="14"/>
       <c r="O2" s="14">
-        <f t="shared" ref="O2:O35" si="1">F2</f>
-        <v>30</v>
+        <f>F2</f>
+        <v>20</v>
       </c>
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
@@ -58900,38 +58800,33 @@
         <v>23</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G3" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="15">
         <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
       <c r="I3" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="14"/>
-      <c r="K3" s="14">
-        <v>15</v>
-      </c>
+      <c r="K3" s="14"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
-      <c r="N3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N3" s="14"/>
       <c r="O3" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f>F3</f>
+        <v>20</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
@@ -58952,17 +58847,17 @@
         <v>28</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G4" s="15">
         <v>1</v>
@@ -58975,18 +58870,13 @@
         <v>1</v>
       </c>
       <c r="J4" s="14"/>
-      <c r="K4" s="14">
-        <v>15</v>
-      </c>
+      <c r="K4" s="14"/>
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N4" s="14"/>
       <c r="O4" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f>F4</f>
+        <v>20</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
@@ -59004,20 +58894,20 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A5" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G5" s="15">
         <v>1</v>
@@ -59030,18 +58920,13 @@
         <v>1</v>
       </c>
       <c r="J5" s="14"/>
-      <c r="K5" s="14">
-        <v>15</v>
-      </c>
+      <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N5" s="14"/>
       <c r="O5" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f>F5</f>
+        <v>25</v>
       </c>
       <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
@@ -59059,20 +58944,20 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A6" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G6" s="15">
         <v>1</v>
@@ -59085,18 +58970,13 @@
         <v>1</v>
       </c>
       <c r="J6" s="14"/>
-      <c r="K6" s="14">
-        <v>15</v>
-      </c>
+      <c r="K6" s="14"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
-      <c r="N6" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N6" s="14"/>
       <c r="O6" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f>F6</f>
+        <v>20</v>
       </c>
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
@@ -59114,20 +58994,20 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A7" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G7" s="15">
         <v>1</v>
@@ -59140,18 +59020,13 @@
         <v>1</v>
       </c>
       <c r="J7" s="14"/>
-      <c r="K7" s="14">
-        <v>15</v>
-      </c>
+      <c r="K7" s="14"/>
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
-      <c r="N7" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N7" s="14"/>
       <c r="O7" s="14">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f>F7</f>
+        <v>20</v>
       </c>
       <c r="P7" s="14"/>
       <c r="Q7" s="14"/>
@@ -59169,20 +59044,20 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A8" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G8" s="15">
         <v>1</v>
@@ -59195,18 +59070,13 @@
         <v>1</v>
       </c>
       <c r="J8" s="14"/>
-      <c r="K8" s="14">
-        <v>20</v>
-      </c>
+      <c r="K8" s="14"/>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
-      <c r="N8" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N8" s="14"/>
       <c r="O8" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f>F8</f>
+        <v>20</v>
       </c>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
@@ -59224,44 +59094,39 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A9" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G9" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="15">
         <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
       <c r="I9" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="14"/>
-      <c r="K9" s="14">
-        <v>20</v>
-      </c>
+      <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
-      <c r="N9" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N9" s="14"/>
       <c r="O9" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f>F9</f>
+        <v>20</v>
       </c>
       <c r="P9" s="14"/>
       <c r="Q9" s="14"/>
@@ -59279,20 +59144,20 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A10" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G10" s="15">
         <v>1</v>
@@ -59305,18 +59170,13 @@
         <v>1</v>
       </c>
       <c r="J10" s="14"/>
-      <c r="K10" s="14">
-        <v>20</v>
-      </c>
+      <c r="K10" s="14"/>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
-      <c r="N10" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N10" s="14"/>
       <c r="O10" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f>F10</f>
+        <v>20</v>
       </c>
       <c r="P10" s="14"/>
       <c r="Q10" s="14"/>
@@ -59334,20 +59194,20 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A11" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="14">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G11" s="15">
         <v>1</v>
@@ -59360,18 +59220,13 @@
         <v>1</v>
       </c>
       <c r="J11" s="14"/>
-      <c r="K11" s="14">
-        <v>20</v>
-      </c>
+      <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
-      <c r="N11" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="N11" s="14"/>
       <c r="O11" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f>F11</f>
+        <v>18</v>
       </c>
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
@@ -59389,20 +59244,20 @@
     </row>
     <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A12" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="14">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G12" s="15">
         <v>1</v>
@@ -59415,19 +59270,11 @@
         <v>1</v>
       </c>
       <c r="J12" s="14"/>
-      <c r="K12" s="14">
-        <v>20</v>
-      </c>
+      <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
-      <c r="N12" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
       <c r="P12" s="14"/>
       <c r="Q12" s="14"/>
       <c r="R12" s="14"/>
@@ -59444,20 +59291,20 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A13" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G13" s="15">
         <v>1</v>
@@ -59470,19 +59317,11 @@
         <v>1</v>
       </c>
       <c r="J13" s="14"/>
-      <c r="K13" s="14">
-        <v>20</v>
-      </c>
+      <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
-      <c r="N13" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
       <c r="P13" s="14"/>
       <c r="Q13" s="14"/>
       <c r="R13" s="14"/>
@@ -59499,20 +59338,20 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A14" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G14" s="15">
         <v>1</v>
@@ -59525,19 +59364,11 @@
         <v>1</v>
       </c>
       <c r="J14" s="14"/>
-      <c r="K14" s="14">
-        <v>20</v>
-      </c>
+      <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
-      <c r="N14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
       <c r="P14" s="14"/>
       <c r="Q14" s="14"/>
       <c r="R14" s="14"/>
@@ -59554,20 +59385,20 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A15" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
@@ -59580,19 +59411,11 @@
         <v>1</v>
       </c>
       <c r="J15" s="14"/>
-      <c r="K15" s="14">
-        <v>20</v>
-      </c>
+      <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
-      <c r="N15" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
       <c r="P15" s="14"/>
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
@@ -59609,20 +59432,20 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A16" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G16" s="15">
         <v>1</v>
@@ -59635,19 +59458,11 @@
         <v>1</v>
       </c>
       <c r="J16" s="14"/>
-      <c r="K16" s="14">
-        <v>20</v>
-      </c>
+      <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="14"/>
-      <c r="N16" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
       <c r="P16" s="14"/>
       <c r="Q16" s="14"/>
       <c r="R16" s="14"/>
@@ -59664,20 +59479,20 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A17" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="14">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
         <v>1</v>
@@ -59690,19 +59505,11 @@
         <v>1</v>
       </c>
       <c r="J17" s="14"/>
-      <c r="K17" s="14">
-        <v>20</v>
-      </c>
+      <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
-      <c r="N17" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
       <c r="P17" s="14"/>
       <c r="Q17" s="14"/>
       <c r="R17" s="14"/>
@@ -59719,45 +59526,37 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A18" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="15">
         <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" s="14"/>
-      <c r="K18" s="14">
-        <v>20</v>
-      </c>
+      <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
       <c r="P18" s="14"/>
       <c r="Q18" s="14"/>
       <c r="R18" s="14"/>
@@ -59774,20 +59573,20 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A19" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G19" s="15">
         <v>1</v>
@@ -59800,19 +59599,11 @@
         <v>1</v>
       </c>
       <c r="J19" s="14"/>
-      <c r="K19" s="14">
-        <v>20</v>
-      </c>
+      <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
@@ -59829,45 +59620,37 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A20" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
         <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="14"/>
-      <c r="K20" s="14">
-        <v>20</v>
-      </c>
+      <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
-      <c r="N20" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
       <c r="P20" s="14"/>
       <c r="Q20" s="14"/>
       <c r="R20" s="14"/>
@@ -59884,20 +59667,20 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A21" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G21" s="15">
         <v>1</v>
@@ -59910,19 +59693,11 @@
         <v>1</v>
       </c>
       <c r="J21" s="14"/>
-      <c r="K21" s="14">
-        <v>20</v>
-      </c>
+      <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
-      <c r="N21" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="14"/>
@@ -59939,20 +59714,20 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A22" s="10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="14">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
@@ -59965,19 +59740,11 @@
         <v>1</v>
       </c>
       <c r="J22" s="14"/>
-      <c r="K22" s="14">
-        <v>20</v>
-      </c>
+      <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
-      <c r="N22" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
       <c r="R22" s="14"/>
@@ -59994,20 +59761,20 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
       <c r="A23" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="14">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
@@ -60020,19 +59787,11 @@
         <v>1</v>
       </c>
       <c r="J23" s="14"/>
-      <c r="K23" s="14">
-        <v>20</v>
-      </c>
+      <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
-      <c r="N23" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
       <c r="R23" s="14"/>
@@ -60047,685 +59806,26 @@
       <c r="AA23" s="24"/>
       <c r="AB23" s="11"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A24" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="14">
-        <v>35</v>
-      </c>
-      <c r="G24" s="15">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="15">
-        <v>1</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14">
-        <v>20</v>
-      </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="11"/>
+    <row r="36" ht="14.8" spans="6:15">
+      <c r="F36" s="16"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="21"/>
+      <c r="O36" s="5"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A25" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="14">
-        <v>35</v>
-      </c>
-      <c r="G25" s="15">
-        <v>1</v>
-      </c>
-      <c r="H25" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-      <c r="I25" s="15">
-        <v>1</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14">
-        <v>20</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="11"/>
+    <row r="37" ht="14.8" spans="6:15">
+      <c r="F37" s="16"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="21"/>
+      <c r="O37" s="5"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A26" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="14">
-        <v>35</v>
-      </c>
-      <c r="G26" s="15">
-        <v>1</v>
-      </c>
-      <c r="H26" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-      <c r="I26" s="15">
-        <v>1</v>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14">
-        <v>20</v>
-      </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="24"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="24"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="11"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="14">
-        <v>35</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-      <c r="I27" s="15">
-        <v>1</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14">
-        <v>20</v>
-      </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="11"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A28" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="14">
-        <v>35</v>
-      </c>
-      <c r="G28" s="15">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="15">
-        <v>1</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14">
-        <v>20</v>
-      </c>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="11"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="11"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A29" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="14">
-        <v>35</v>
-      </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <v>1</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14">
-        <v>20</v>
-      </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="11"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A30" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="14">
-        <v>35</v>
-      </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>2</v>
-      </c>
-      <c r="I30" s="15">
-        <v>1</v>
-      </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="24"/>
-      <c r="AB30" s="11"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A31" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="14">
-        <v>35</v>
-      </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="15">
-        <v>1</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14">
-        <f>F31</f>
-        <v>35</v>
-      </c>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="11"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
-      <c r="AA31" s="24"/>
-      <c r="AB31" s="11"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A32" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="14">
-        <v>35</v>
-      </c>
-      <c r="G32" s="15">
-        <v>1</v>
-      </c>
-      <c r="H32" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="15">
-        <v>1</v>
-      </c>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14">
-        <f>F32</f>
-        <v>35</v>
-      </c>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
-      <c r="AA32" s="24"/>
-      <c r="AB32" s="11"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A33" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="14">
-        <v>40</v>
-      </c>
-      <c r="G33" s="15">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <f>SUMIFS([1]!VENTAS[Cantidad],[1]!VENTAS[Código del producto Vendido],[1]!STOCK[[#This Row],[Code]])</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="15">
-        <v>1</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14">
-        <f>F33</f>
-        <v>40</v>
-      </c>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="24"/>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="24"/>
-      <c r="AA33" s="24"/>
-      <c r="AB33" s="11"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="11"/>
-      <c r="W34" s="24"/>
-      <c r="X34" s="24"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="24"/>
-      <c r="AA34" s="24"/>
-      <c r="AB34" s="11"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="24"/>
-      <c r="X35" s="24"/>
-      <c r="Y35" s="24"/>
-      <c r="Z35" s="24"/>
-      <c r="AA35" s="24"/>
-      <c r="AB35" s="11"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="11"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="11"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
-      <c r="AA37" s="24"/>
-      <c r="AB37" s="11"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="20" customHeight="1" spans="1:28">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="11"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="11"/>
+    <row r="38" ht="14.8" spans="6:15">
+      <c r="F38" s="16"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="21"/>
+      <c r="O38" s="5"/>
     </row>
     <row r="39" ht="14.8" spans="6:15">
       <c r="F39" s="16"/>
@@ -60771,47 +59871,37 @@
     </row>
     <row r="45" ht="14.8" spans="6:15">
       <c r="F45" s="16"/>
-      <c r="G45" s="17"/>
       <c r="H45" s="18"/>
       <c r="I45" s="21"/>
       <c r="O45" s="5"/>
     </row>
     <row r="46" ht="14.8" spans="6:15">
       <c r="F46" s="16"/>
-      <c r="G46" s="17"/>
       <c r="H46" s="18"/>
       <c r="I46" s="21"/>
       <c r="O46" s="5"/>
     </row>
-    <row r="47" ht="14.8" spans="6:15">
-      <c r="F47" s="16"/>
-      <c r="G47" s="17"/>
+    <row r="47" ht="14.8" spans="8:15">
       <c r="H47" s="18"/>
       <c r="I47" s="21"/>
       <c r="O47" s="5"/>
     </row>
-    <row r="48" ht="14.8" spans="6:15">
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
+    <row r="48" ht="14.8" spans="8:15">
       <c r="H48" s="18"/>
       <c r="I48" s="21"/>
       <c r="O48" s="5"/>
     </row>
-    <row r="49" ht="14.8" spans="6:15">
-      <c r="F49" s="16"/>
-      <c r="G49" s="17"/>
+    <row r="49" ht="14.8" spans="8:15">
       <c r="H49" s="18"/>
       <c r="I49" s="21"/>
       <c r="O49" s="5"/>
     </row>
-    <row r="50" ht="14.8" spans="6:15">
-      <c r="F50" s="16"/>
+    <row r="50" ht="14.8" spans="8:15">
       <c r="H50" s="18"/>
       <c r="I50" s="21"/>
       <c r="O50" s="5"/>
     </row>
-    <row r="51" ht="14.8" spans="6:15">
-      <c r="F51" s="16"/>
+    <row r="51" ht="14.8" spans="8:15">
       <c r="H51" s="18"/>
       <c r="I51" s="21"/>
       <c r="O51" s="5"/>
@@ -60848,41 +59938,16 @@
     </row>
     <row r="58" ht="14.8" spans="8:15">
       <c r="H58" s="18"/>
-      <c r="I58" s="21"/>
       <c r="O58" s="5"/>
     </row>
-    <row r="59" ht="14.8" spans="8:15">
+    <row r="59" ht="14.8" spans="8:8">
       <c r="H59" s="18"/>
-      <c r="I59" s="21"/>
-      <c r="O59" s="5"/>
     </row>
-    <row r="60" ht="14.8" spans="8:15">
+    <row r="60" ht="14.8" spans="8:8">
       <c r="H60" s="18"/>
-      <c r="I60" s="21"/>
-      <c r="O60" s="5"/>
     </row>
-    <row r="61" ht="14.8" spans="8:15">
+    <row r="61" ht="14.8" spans="8:8">
       <c r="H61" s="18"/>
-      <c r="I61" s="21"/>
-      <c r="O61" s="5"/>
-    </row>
-    <row r="62" ht="14.8" spans="8:15">
-      <c r="H62" s="18"/>
-      <c r="I62" s="21"/>
-      <c r="O62" s="5"/>
-    </row>
-    <row r="63" ht="14.8" spans="8:15">
-      <c r="H63" s="18"/>
-      <c r="O63" s="5"/>
-    </row>
-    <row r="64" ht="14.8" spans="8:8">
-      <c r="H64" s="18"/>
-    </row>
-    <row r="65" ht="14.8" spans="8:8">
-      <c r="H65" s="18"/>
-    </row>
-    <row r="66" ht="14.8" spans="8:8">
-      <c r="H66" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
